--- a/src/main/resources/python/MultifacetedModeling/Results/OnTrain/DKNCOR/KNN.xlsx
+++ b/src/main/resources/python/MultifacetedModeling/Results/OnTrain/DKNCOR/KNN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="result0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="result0" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,436 +466,381 @@
           <t>Time</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>d_class</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[1, 2, 8, 11, 15, 16, 17, 19, 27, 29, 30, 31, 32, 36, 37, 43, 44]</t>
+          <t>[1, 2, 6, 7, 12, 14, 15, 18, 23, 24, 25, 28, 31, 33, 35, 38]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.4924603174603175</t>
+          <t>0.14285714285714285</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.07342086505154374</t>
+          <t>0.07440650388876133</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.10779761754747942</t>
+          <t>0.12125550429900205</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.8278822091096121</t>
+          <t>0.7990186696518851</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.7475523948669434</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.428680896759033</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[1, 2, 4, 8, 10, 16, 18, 19, 20, 26, 31, 32, 33, 36, 39, 42, 44]</t>
+          <t>[2, 3, 4, 7, 9, 12, 15, 17, 20, 22, 26, 27, 28, 29, 31, 32, 34, 36, 37, 38, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.581547619047619</t>
+          <t>0.6186813186813187</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.07992871820700787</t>
+          <t>0.08052371093396238</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.09542930978091473</t>
+          <t>0.11193473242488627</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.8651127180145352</t>
+          <t>0.8287295167477169</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.6665306091308594</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>4.414464473724365</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 6, 15, 18, 19, 20, 26, 28, 29, 34, 35, 36, 37, 41]</t>
+          <t>[1, 9, 11, 12, 13, 14, 17, 19, 21, 26, 29, 30, 31, 33, 34, 35, 37, 38, 39, 40, 41, 42]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.5878968253968254</t>
+          <t>0.639010989010989</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.07866257193854129</t>
+          <t>0.0755776103759507</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.060666547293809416</t>
+          <t>0.1310196080566283</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.945486257845393</t>
+          <t>0.7653473927488084</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.7241134643554688</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.769443988800049</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[0, 8, 10, 11, 13, 14, 15, 18, 21, 23, 24, 26, 29, 31, 32, 34, 35, 37, 44]</t>
+          <t>[7, 9, 13, 15, 16, 20, 21, 22, 25, 31, 32, 35, 36, 39, 41, 43]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.39940476190476193</t>
+          <t>0.45219780219780226</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.08302671751470363</t>
+          <t>0.07081700176874409</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.10462875935727362</t>
+          <t>0.07870907541548226</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.8378527492135043</t>
+          <t>0.915315795175502</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.6380655765533447</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>4.365401029586792</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[2, 7, 11, 16, 19, 25, 27, 28, 31, 32, 35, 36, 37, 38, 40, 41, 43]</t>
+          <t>[2, 3, 5, 9, 11, 12, 13, 16, 17, 21, 24, 25, 28, 29, 31, 33, 35, 39, 41]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.8305555555555555</t>
+          <t>0.30659340659340656</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.07720431658750548</t>
+          <t>0.0759518295544721</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.07506135806497226</t>
+          <t>0.15087728445889997</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.9165473227841168</t>
+          <t>0.6888280008666763</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.707963705062866</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.693008899688721</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[0, 15, 16, 19, 21, 22, 24, 26, 29, 32, 33, 34, 35, 36, 37, 41]</t>
+          <t>[1, 7, 8, 10, 11, 13, 14, 17, 19, 22, 26, 28, 31, 32, 33, 37, 42]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.5559523809523809</t>
+          <t>0.6725274725274726</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.07601176291536953</t>
+          <t>0.07611756727399856</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.09225122459511814</t>
+          <t>0.05830391928624988</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.8739474260850512</t>
+          <t>0.9535326086956522</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.572042465209961</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.772624731063843</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[1, 3, 7, 8, 10, 12, 13, 14, 16, 17, 19, 20, 22, 24, 27, 28, 29, 30, 31, 32, 35, 36, 37, 42, 44]</t>
+          <t>[2, 4, 7, 8, 10, 11, 17, 19, 23, 26, 30, 33, 37, 38, 41, 43]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.9757936507936507</t>
+          <t>0.43186813186813183</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.07964582909624882</t>
+          <t>0.07572547949810093</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.10260328991782298</t>
+          <t>0.14758104423753465</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.8440698807343757</t>
+          <t>0.7022759280658675</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.709071159362793</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>4.914300918579102</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[1, 3, 6, 8, 10, 13, 14, 18, 20, 21, 23, 24, 26, 28, 31, 33, 34, 35, 37, 44]</t>
+          <t>[0, 1, 3, 4, 5, 11, 13, 14, 15, 17, 18, 19, 21, 22, 24, 26, 27, 29, 31, 32, 33, 34, 35, 36, 37, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.6125</t>
+          <t>0.843956043956044</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.0801824386057884</t>
+          <t>0.0739923535481268</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.09639690928906071</t>
+          <t>0.07717153062517071</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.8623634882064767</t>
+          <t>0.9185920121334682</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.6955275535583496</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>5.436383962631226</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[0, 3, 9, 12, 14, 15, 16, 17, 21, 28, 31, 32, 35, 36, 37, 39, 41, 44]</t>
+          <t>[2, 3, 14, 17, 19, 21, 22, 25, 26, 28, 29, 30, 31, 32, 34, 37, 39, 40, 42, 43]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.5767857142857142</t>
+          <t>0.3983516483516484</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.07355699632188335</t>
+          <t>0.07267564727304823</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.06272086220051333</t>
+          <t>0.1242405760807873</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.9417318166877964</t>
+          <t>0.7890013361259569</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.637300968170166</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.803676605224609</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4, 6, 8, 14, 16, 23, 25, 28, 32, 33, 34, 35, 36, 37, 38, 40, 41, 42, 44]</t>
+          <t>[0, 3, 5, 9, 10, 11, 14, 16, 18, 19, 20, 21, 22, 23, 26, 27, 28, 31, 33, 36, 37, 38, 43, 44]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.0069444444444444</t>
+          <t>0.8203296703296703</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.0805567976818021</t>
+          <t>0.07810110422467806</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.07860892701779881</t>
+          <t>0.07490237390528968</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.9084725896013871</t>
+          <t>0.9233090784342048</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.5707876682281494</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.998611688613892</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[0, 2, 5, 6, 8, 12, 14, 15, 16, 20, 23, 25, 27, 29, 31, 35, 37, 43, 44]</t>
+          <t>[1, 8, 10, 15, 17, 22, 24, 25, 28, 29, 31, 32, 33, 34, 36, 37, 38, 40, 43]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -905,711 +850,626 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.4353174603174603</t>
+          <t>0.478021978021978</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.07834509847515639</t>
+          <t>0.07956509686472103</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.1103490607977956</t>
+          <t>0.1061882477342811</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.8196381336964518</t>
+          <t>0.8458634262602918</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.5038137435913086</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>4.88497257232666</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[2, 3, 5, 6, 8, 9, 13, 25, 26, 27, 28, 30, 31, 32, 33, 34, 35, 37, 40]</t>
+          <t>[3, 6, 9, 12, 13, 15, 16, 18, 19, 23, 25, 28, 29, 30, 31, 33, 34, 35, 40, 42, 43]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.7222222222222221</t>
+          <t>0.30659340659340656</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.0787496150148825</t>
+          <t>0.07547435490296339</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.05837919874857391</t>
+          <t>0.08618216843597692</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.9495194941384546</t>
+          <t>0.8984715802397805</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.5290071964263916</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.882227659225464</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 6, 12, 14, 28, 29, 30, 31, 32, 33, 34, 35, 37, 40, 42]</t>
+          <t>[2, 3, 4, 5, 6, 7, 9, 10, 12, 14, 16, 19, 23, 25, 26, 27, 29, 30, 31, 33, 35, 36, 37, 39, 40, 41, 43]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.4744047619047619</t>
+          <t>0.8538461538461538</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.07979547796895299</t>
+          <t>0.07499656972603508</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.06055267772490876</t>
+          <t>0.13613929424886614</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.9456907076114007</t>
+          <t>0.7466506572295248</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.565580368041992</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.877938508987427</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 7, 8, 11, 13, 14, 16, 29, 33, 35, 36, 37, 39, 41, 42]</t>
+          <t>[0, 1, 3, 9, 10, 12, 14, 17, 18, 19, 20, 22, 30, 31, 33, 34, 35, 36, 41]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.9305555555555556</t>
+          <t>0.4807692307692308</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.07189309588911517</t>
+          <t>0.07406224443040922</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.08241529232533962</t>
+          <t>0.13603325417765247</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.8993941939309831</t>
+          <t>0.74704517550195</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.577333688735962</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>6.070153474807739</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[6, 7, 8, 14, 16, 19, 21, 23, 24, 25, 26, 29, 31, 34, 36, 37, 38, 40, 42, 43, 44]</t>
+          <t>[1, 2, 3, 4, 5, 8, 9, 11, 12, 13, 14, 15, 17, 18, 23, 24, 26, 27, 28, 35, 36, 37, 40, 41, 43]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.522420634920635</t>
+          <t>0.9483516483516483</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.07641615574940744</t>
+          <t>0.07222238684883003</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.12321624953820876</t>
+          <t>0.13635112698989502</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.7751238437338592</t>
+          <t>0.7458616206846742</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.6251049041748047</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>5.749662637710571</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[1, 3, 8, 11, 12, 13, 14, 15, 16, 19, 21, 22, 23, 25, 27, 29, 32, 34, 36, 38, 44]</t>
+          <t>[0, 1, 3, 5, 6, 8, 9, 11, 12, 16, 17, 18, 20, 22, 23, 24, 26, 27, 28, 30, 31, 33, 35, 36, 39, 41, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.6047619047619048</t>
+          <t>1.3148351648351646</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.075302081305473</t>
+          <t>0.07658736438849965</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.10417503189495586</t>
+          <t>0.13432055786384314</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.8392560180620119</t>
+          <t>0.7533746208291203</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.516969919204712</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>5.212941408157349</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[2, 3, 6, 7, 12, 14, 16, 17, 19, 21, 22, 27, 30, 32, 33, 34, 35, 37, 41]</t>
+          <t>[1, 2, 3, 4, 5, 11, 14, 16, 17, 20, 21, 23, 25, 26, 27, 29, 31, 33, 35, 39, 42, 43]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.5777777777777777</t>
+          <t>0.6131868131868131</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.08211594741932905</t>
+          <t>0.07620746182590876</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.08586489882401951</t>
+          <t>0.12733309944210539</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.8907959454383246</t>
+          <t>0.7783664957388415</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.4673755168914795</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>4.7869391441345215</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[3, 13, 15, 19, 21, 22, 23, 25, 29, 32, 33, 34, 35, 36, 37, 38, 40, 43, 44]</t>
+          <t>[3, 6, 9, 11, 13, 15, 18, 20, 24, 26, 28, 29, 30, 31, 33, 36, 37, 39, 40, 43]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.6988095238095238</t>
+          <t>0.4423076923076923</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.07355347974166238</t>
+          <t>0.07253062415873553</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.06055267772490876</t>
+          <t>0.10365275719966409</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.9456907076114007</t>
+          <t>0.8531362848476094</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.631934642791748</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.732728719711304</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 6, 11, 13, 16, 18, 19, 21, 22, 24, 25, 26, 27, 28, 29, 30, 31, 32, 35, 37, 39, 42, 43, 44]</t>
+          <t>[9, 11, 12, 13, 14, 16, 19, 20, 21, 23, 24, 25, 26, 31, 32, 33, 34, 36, 37, 38, 40, 41, 44]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.9892857142857143</t>
+          <t>0.6208791208791209</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.07934098477705558</t>
+          <t>0.07652566250038695</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.11093126208293234</t>
+          <t>0.1098932593419977</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.8177299358803797</t>
+          <t>0.8349198324425827</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2.617199659347534</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>4.78196382522583</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[3, 4, 11, 13, 14, 15, 16, 17, 19, 21, 23, 28, 29, 31, 32, 33, 34, 36, 37, 39, 42, 44]</t>
+          <t>[1, 2, 3, 5, 9, 11, 12, 15, 16, 20, 24, 25, 28, 30, 31, 33, 34, 36]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.7765873015873016</t>
+          <t>0.29395604395604397</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.07069838660741054</t>
+          <t>0.07080711051325538</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.08699772850415452</t>
+          <t>0.08098003309408942</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.887895443454912</t>
+          <t>0.9103585873176369</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.636828660964966</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>5.221465110778809</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[1, 5, 7, 9, 11, 14, 20, 25, 27, 29, 31, 32, 33, 34, 35, 37, 38, 39, 41, 42, 43, 44]</t>
+          <t>[1, 4, 5, 9, 11, 12, 18, 22, 25, 26, 28, 31, 33, 34, 37, 39, 40, 41]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.8303571428571428</t>
+          <t>0.5291208791208791</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.07946527248958599</t>
+          <t>0.07538657850358721</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.061184028966318034</t>
+          <t>0.1376745330065594</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.9445522941415849</t>
+          <t>0.7409044128268092</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.4761838912963867</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.874756813049316</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[3, 7, 9, 12, 15, 16, 18, 19, 22, 23, 24, 25, 26, 27, 30, 32, 33, 34, 35, 38, 41, 42]</t>
+          <t>[3, 4, 5, 6, 9, 12, 15, 18, 19, 20, 22, 25, 26, 28, 30, 31, 32, 33, 35, 37, 40, 41, 43]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.5371031746031746</t>
+          <t>0.7104395604395605</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.07946201392807742</t>
+          <t>0.07111962726212895</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.09080867504474317</t>
+          <t>0.10681859043233084</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.8778588185781687</t>
+          <t>0.8440280586450961</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.515263557434082</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>4.984561204910278</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[4, 7, 10, 11, 13, 15, 16, 19, 25, 26, 27, 29, 31, 32, 33, 35, 36, 37, 38, 39]</t>
+          <t>[2, 3, 5, 10, 11, 12, 15, 18, 20, 22, 24, 25, 26, 29, 32, 33, 34, 36, 37, 40, 42, 44]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.6454365079365079</t>
+          <t>0.6516483516483516</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.07346800595381475</t>
+          <t>0.07412730273522017</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.05778869457132317</t>
+          <t>0.11539629569503386</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.9505355475210384</t>
+          <t>0.8179726996966633</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.5500383377075195</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>5.08951997756958</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[8, 9, 11, 16, 17, 18, 22, 24, 25, 28, 31, 32, 33, 35, 36, 37, 38, 40, 41, 43, 44]</t>
+          <t>[2, 3, 5, 6, 8, 12, 14, 15, 17, 18, 20, 24, 26, 30, 31, 33, 35, 37, 39, 43]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.9119047619047619</t>
+          <t>0.40384615384615385</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.07387596175410185</t>
+          <t>0.07802668126402965</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.07747176272826845</t>
+          <t>0.12679982678944504</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.9111015244713653</t>
+          <t>0.7802190163224036</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2.584043264389038</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>5.245388031005859</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[0, 6, 8, 12, 17, 19, 21, 23, 26, 29, 32, 33, 34, 35, 37, 39, 44]</t>
+          <t>[1, 2, 3, 5, 7, 12, 13, 18, 19, 22, 23, 25, 27, 29, 31, 32, 34, 35, 36, 37, 38, 39, 44]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.44107142857142856</t>
+          <t>0.5857142857142856</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.06999040850979213</t>
+          <t>0.0785248488739507</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.10444269917619857</t>
+          <t>0.13000525985146555</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.8384289258267987</t>
+          <t>0.7689666690741008</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2.5340633392333984</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>5.214552640914917</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[0, 6, 15, 18, 19, 23, 29, 30, 33, 34, 35, 36, 39, 43]</t>
+          <t>[0, 1, 4, 9, 12, 15, 18, 20, 26, 27, 31, 32, 35, 36, 37, 39, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.27162698412698416</t>
+          <t>0.49340659340659343</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.07082470248173563</t>
+          <t>0.07544368249733528</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.07096232350726947</t>
+          <t>0.09283428363060739</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.9254130080919065</t>
+          <t>0.8821934132601473</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2.5919811725616455</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>5.312405586242676</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[1, 2, 8, 16, 17, 20, 21, 25, 27, 31, 32, 33, 34, 35, 36, 37, 39, 40, 41, 42, 43]</t>
+          <t>[1, 6, 7, 11, 14, 16, 18, 22, 23, 26, 27, 28, 29, 30, 33, 34, 35, 36, 39, 40, 41, 42]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.8841269841269841</t>
+          <t>0.6445054945054945</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.07599400443128693</t>
+          <t>0.07462392928903891</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.05908426128756807</t>
+          <t>0.131854972431878</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.9482927955424082</t>
+          <t>0.7623456232847031</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.708024501800537</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.208721876144409</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[0, 3, 6, 8, 14, 17, 18, 20, 21, 22, 24, 25, 26, 29, 32, 33, 34, 37, 40, 41, 43, 44]</t>
+          <t>[1, 3, 7, 11, 16, 18, 19, 20, 22, 26, 27, 31, 32, 33, 34, 35, 37, 39, 41, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1619,207 +1479,182 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.6047619047619048</t>
+          <t>0.7928571428571429</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.0800964699052844</t>
+          <t>0.07531819884276957</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.10024328252714709</t>
+          <t>0.10051829890820302</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.8511605703463712</t>
+          <t>0.8618842987144302</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2.6488428115844727</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>5.250644207000732</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[2, 4, 5, 7, 12, 15, 19, 23, 31, 33, 36, 37, 42]</t>
+          <t>[0, 1, 6, 9, 12, 13, 14, 17, 19, 22, 26, 28, 29, 31, 33, 35, 36, 41]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.39384920634920634</t>
+          <t>0.40384615384615385</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.0747718982510257</t>
+          <t>0.07368204336985745</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.07607428802843781</t>
+          <t>0.07228507028567357</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.9142797890156673</t>
+          <t>0.9285750397226635</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.4652464389801025</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>5.231403589248657</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[0, 1, 4, 5, 6, 8, 12, 14, 15, 17, 19, 20, 24, 25, 26, 28, 29, 30, 31, 32, 33, 34, 35, 37, 40]</t>
+          <t>[1, 2, 3, 9, 10, 11, 12, 14, 15, 17, 18, 19, 22, 23, 25, 26, 27, 28, 29, 31, 33, 34, 35, 36, 37, 39, 41]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.9109126984126985</t>
+          <t>1.1043956043956045</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.0777709173297493</t>
+          <t>0.07473984662372377</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.08317309584088001</t>
+          <t>0.12121927850147167</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.8975355596945493</t>
+          <t>0.7991387404304492</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2.594782829284668</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.353787422180176</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[0, 3, 5, 8, 11, 13, 14, 15, 17, 20, 21, 22, 23, 25, 27, 31, 32, 33, 35, 36, 37, 39, 40, 43, 44]</t>
+          <t>[1, 2, 3, 4, 5, 7, 9, 10, 12, 13, 14, 15, 17, 18, 20, 22, 23, 26, 33, 34, 35, 40, 41, 43]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.9444444444444444</t>
+          <t>0.4956043956043956</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.07931327714054737</t>
+          <t>0.07118703326786575</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.053218058521531886</t>
+          <t>0.15499210978763628</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.9580506252836862</t>
+          <t>0.6716235735952621</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.484279155731201</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.340856552124023</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[1, 4, 14, 15, 16, 17, 20, 21, 24, 25, 27, 28, 32, 33, 34, 36, 40, 44]</t>
+          <t>[1, 5, 6, 8, 9, 11, 12, 14, 15, 21, 22, 23, 25, 27, 28, 29, 30, 31, 33, 34, 35, 36, 38, 42]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.4833333333333333</t>
+          <t>0.9357142857142857</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.07320209896186688</t>
+          <t>0.07898692668764166</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.08532450792618912</t>
+          <t>0.05945359297609968</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.8921661719004068</t>
+          <t>0.9516819939974641</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2.515033721923828</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>5.284181833267212</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 4, 6, 15, 16, 17, 18, 20, 21, 25, 31, 32, 34, 37, 40, 41, 43, 44]</t>
+          <t>[1, 3, 10, 13, 15, 16, 17, 20, 21, 25, 26, 29, 30, 31, 36, 37, 40, 41, 42, 43]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1829,2013 +1664,1773 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.4978174603174603</t>
+          <t>0.4346153846153846</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.07875029084718228</t>
+          <t>0.07290411346361417</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.1137589974758368</t>
+          <t>0.11464899788597019</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.8083190511965692</t>
+          <t>0.8203226563628485</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.5879151821136475</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>5.233770370483398</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[8, 10, 11, 12, 14, 16, 19, 21, 25, 26, 28, 29, 30, 33, 34, 35, 36, 38, 39, 41, 42]</t>
+          <t>[1, 2, 3, 5, 8, 9, 11, 12, 16, 18, 22, 24, 25, 28, 29, 31, 32, 33, 34, 35, 36, 37]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.8615079365079364</t>
+          <t>0.8186813186813187</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.08208456685992369</t>
+          <t>0.07242361532681642</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.09878847403250908</t>
+          <t>0.07000988539111734</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.8554493688469424</t>
+          <t>0.9330005055611729</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.588315010070801</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>5.304134368896484</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[0, 1, 3, 4, 5, 7, 9, 10, 13, 17, 19, 20, 22, 23, 27, 28, 31, 33, 34, 36, 37, 42]</t>
+          <t>[3, 5, 6, 7, 13, 14, 15, 17, 18, 19, 20, 25, 26, 28, 30, 31, 32, 34, 35, 36, 40]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.9238095238095239</t>
+          <t>0.4675824175824176</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.07826682188400816</t>
+          <t>0.0770362280346283</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.07359256925455192</t>
+          <t>0.07104185294030571</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.9197813463555118</t>
+          <t>0.9310107612306804</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.4594082832336426</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.312619924545288</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[3, 6, 12, 16, 17, 20, 23, 25, 26, 28, 35, 37, 38, 40, 41, 42]</t>
+          <t>[1, 2, 5, 6, 11, 12, 13, 14, 15, 16, 18, 19, 20, 24, 25, 26, 27, 31, 35, 37, 38]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.5097222222222222</t>
+          <t>0.3752747252747253</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.07485485563437752</t>
+          <t>0.07397795298168712</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.09082556268426892</t>
+          <t>0.07959685942904601</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.8778133852968337</t>
+          <t>0.9133946627184747</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.531970500946045</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>5.30053448677063</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[9, 10, 11, 15, 16, 17, 18, 19, 20, 23, 28, 29, 32, 35, 37]</t>
+          <t>[1, 2, 3, 4, 8, 10, 11, 12, 13, 14, 19, 20, 23, 26, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 43]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.5035714285714286</t>
+          <t>1.0692307692307692</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.0821387674386687</t>
+          <t>0.07448668280539474</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.06056044836051661</t>
+          <t>0.13093338257308254</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.9456767678546274</t>
+          <t>0.765656146179402</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2.556154251098633</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.217483282089233</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[0, 1, 10, 16, 17, 19, 20, 23, 24, 27, 29, 30, 31, 32, 33, 34, 37, 38, 40, 43, 44]</t>
+          <t>[1, 3, 5, 9, 11, 14, 15, 19, 20, 21, 22, 24, 25, 26, 27, 29, 30, 31, 32, 33, 34, 36, 37, 40, 41, 42, 44]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.5569444444444445</t>
+          <t>0.856043956043956</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.07372254489214837</t>
+          <t>0.07458953515946039</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.08039489694159282</t>
+          <t>0.10367091481690063</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.9042663970668795</t>
+          <t>0.8530848259425104</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2.627885103225708</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>5.318628787994385</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[6, 11, 12, 15, 16, 17, 21, 23, 24, 26, 27, 31, 36, 38, 41, 43, 44]</t>
+          <t>[3, 5, 8, 9, 11, 13, 14, 16, 17, 18, 21, 23, 24, 27, 29, 30, 31, 32, 34, 36, 37, 40, 41, 43]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.2359126984126984</t>
+          <t>0.6747252747252748</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.07461418650617935</t>
+          <t>0.07751699177251119</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.12829522906326551</t>
+          <t>0.11784419720695878</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.7562029472069619</t>
+          <t>0.8101680990899899</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2.610180139541626</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>5.2667717933654785</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 6, 12, 15, 16, 17, 18, 19, 21, 22, 23, 24, 25, 26, 28, 30, 31, 32, 33, 34, 36, 38, 40, 42, 44]</t>
+          <t>[1, 3, 5, 11, 12, 13, 14, 17, 18, 20, 24, 25, 26, 27, 28, 30, 31, 35, 36, 41, 43]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.8595238095238095</t>
+          <t>0.5291208791208791</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.08064051885299414</t>
+          <t>0.07598386220873976</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.09993124042367438</t>
+          <t>0.1309046281239441</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.852085757166285</t>
+          <t>0.7657590639895999</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2.558645725250244</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>5.527310848236084</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[6, 11, 14, 17, 20, 25, 26, 28, 29, 31, 32, 34, 36, 40, 41, 43]</t>
+          <t>[3, 5, 9, 10, 11, 14, 15, 16, 17, 18, 19, 21, 24, 26, 30, 31, 32, 33, 34, 35, 37, 40, 41]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.5035714285714286</t>
+          <t>0.4906593406593407</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.07627292698697695</t>
+          <t>0.07328615615537036</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.08445401126658976</t>
+          <t>0.0818661819190782</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.8943552300010956</t>
+          <t>0.9083859959555106</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.5286905765533447</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.174710035324097</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 13, 14, 18, 20, 22, 23, 25, 27, 29, 30, 31, 33, 34, 35, 37, 40, 42, 43, 44]</t>
+          <t>[1, 3, 7, 11, 14, 15, 18, 19, 20, 21, 26, 28, 30, 32, 34, 36, 37, 38, 40, 41]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.489484126984127</t>
+          <t>0.5934065934065934</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.07587256866804738</t>
+          <t>0.0777229811786998</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.07326145922444877</t>
+          <t>0.1212503298477099</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.9205015671221299</t>
+          <t>0.7990358226202513</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2.580496072769165</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.25692081451416</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 13, 16, 17, 19, 22, 26, 27, 28, 29, 30, 31, 33, 34, 35, 37, 40]</t>
+          <t>[0, 2, 3, 6, 8, 11, 12, 13, 15, 16, 21, 22, 23, 24, 25, 26, 29, 30, 31, 33, 34, 35, 36, 37, 41, 43]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.7325396825396826</t>
+          <t>0.7417582417582418</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.06634025889819066</t>
+          <t>0.07477297236888396</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0714645151895739</t>
+          <t>0.09688221203523617</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.9243535865771392</t>
+          <t>0.8716957966199624</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2.602701425552368</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>5.401955842971802</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[2, 4, 5, 6, 7, 8, 14, 15, 17, 24, 25, 26, 31, 32, 34, 35, 37]</t>
+          <t>[2, 8, 9, 10, 11, 12, 14, 16, 17, 19, 24, 25, 26, 27, 30, 31, 35, 36, 37, 40, 43, 44]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.45277777777777783</t>
+          <t>0.6923076923076923</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.07613858493197037</t>
+          <t>0.07540933811512</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.07636240246989011</t>
+          <t>0.09554539188436113</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.9136292670329155</t>
+          <t>0.875212155135057</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2.599398374557495</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.370279312133789</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[3, 4, 5, 11, 13, 14, 15, 17, 20, 25, 27, 30, 31, 32, 34, 35, 37, 39]</t>
+          <t>[1, 4, 5, 6, 9, 10, 11, 15, 16, 17, 19, 21, 22, 23, 24, 25, 28, 29, 31, 33, 34, 35, 37, 40, 41, 43]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0.4902777777777778</t>
+          <t>0.6489010989010989</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.07812233898511396</t>
+          <t>0.07038979632850761</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.07238048471169645</t>
+          <t>0.0732593181720855</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.9224020206288835</t>
+          <t>0.92663675429727</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.651223659515381</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.392870187759399</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[1, 6, 7, 12, 13, 17, 18, 19, 20, 22, 24, 25, 26, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 44]</t>
+          <t>[0, 1, 2, 3, 6, 9, 10, 11, 12, 13, 14, 15, 17, 18, 19, 20, 22, 25, 27, 28, 29, 30, 32, 33, 34, 35, 36, 37, 40, 43]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.0119047619047619</t>
+          <t>1.2736263736263735</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.07642083016166754</t>
+          <t>0.07383023783294962</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.07892047505816491</t>
+          <t>0.11051382457925457</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.9077456571000263</t>
+          <t>0.8330501588906544</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2.6087026596069336</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.2323384284973145</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 6, 7, 8, 11, 14, 15, 16, 20, 23, 24, 25, 28, 29, 31, 32, 33, 35, 37, 38, 40, 41, 42]</t>
+          <t>[1, 3, 6, 8, 9, 11, 13, 14, 15, 16, 18, 19, 22, 24, 31, 33, 34, 36, 38, 39, 40]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0.8414682539682539</t>
+          <t>0.8873626373626373</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0.07811705037551236</t>
+          <t>0.08023406512836735</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.0622690854033325</t>
+          <t>0.1042094895530251</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.9425682020941917</t>
+          <t>0.8515543999871603</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2.556776285171509</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.296736240386963</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[3, 5, 6, 7, 8, 11, 12, 13, 14, 19, 22, 25, 27, 29, 30, 32, 33, 34, 35, 36, 37, 38, 39, 41, 42]</t>
+          <t>[0, 1, 2, 4, 8, 9, 13, 17, 20, 22, 25, 26, 30, 31, 33, 34, 36, 39, 40, 43]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.010515873015873</t>
+          <t>0.45219780219780226</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.08068793316201042</t>
+          <t>0.07302531850802894</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.05928038775593785</t>
+          <t>0.13626367077656582</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.9479489482086679</t>
+          <t>0.7461875270836342</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2.6243441104888916</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.362679481506348</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[1, 2, 15, 17, 20, 24, 27, 28, 29, 31, 35, 37, 39, 40, 44]</t>
+          <t>[4, 5, 7, 8, 9, 11, 12, 16, 17, 19, 22, 25, 26, 29, 31, 33, 34, 36, 37, 43]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0.44305555555555554</t>
+          <t>0.7230769230769231</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0.07456955907908507</t>
+          <t>0.07634363144100297</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.10584499774916022</t>
+          <t>0.07214606040647795</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.8340611353711792</t>
+          <t>0.9288494872165246</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2.6051840782165527</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>5.3310253620147705</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 6, 7, 8, 12, 14, 15, 16, 17, 22, 23, 26, 29, 31, 32, 33, 34, 35, 37, 38, 43, 44]</t>
+          <t>[0, 1, 4, 5, 6, 8, 9, 14, 15, 17, 18, 19, 21, 22, 23, 24, 26, 28, 29, 30, 32, 33, 35, 36, 37, 40, 41]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0.6761904761904762</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.07842693547905158</t>
+          <t>0.07334495411901282</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.10418005070951655</t>
+          <t>0.12685919000748613</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.839240529443375</t>
+          <t>0.7800131807020078</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2.6449146270751953</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>5.645639896392822</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 4, 5, 8, 9, 12, 14, 15, 16, 19, 20, 23, 24, 25, 26, 27, 28, 31, 33, 34, 35, 37, 39, 40, 44]</t>
+          <t>[1, 3, 4, 5, 9, 10, 11, 12, 15, 16, 17, 18, 19, 20, 23, 25, 29, 30, 33, 34, 35, 36, 39, 41, 43]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.019047619047619</t>
+          <t>0.8027472527472528</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.07829259967437277</t>
+          <t>0.0734693515728574</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.09901737836254083</t>
+          <t>0.08972047776982053</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.8547787116599626</t>
+          <t>0.8899637079300882</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2.610215663909912</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>5.305085897445679</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>[6, 12, 16, 17, 19, 20, 23, 26, 27, 28, 30, 31, 32, 33, 34, 37, 38, 44]</t>
+          <t>[1, 2, 3, 4, 5, 9, 10, 14, 15, 16, 25, 28, 29, 30, 31, 33, 35, 36, 37, 40, 41]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0.5994047619047619</t>
+          <t>0.6186813186813187</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.07216983830605662</t>
+          <t>0.07686981252618467</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.08430529832982185</t>
+          <t>0.14064570045923402</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.8947269568483824</t>
+          <t>0.7296006066734075</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2.6447737216949463</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>5.305551528930664</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>[1, 2, 10, 13, 14, 16, 17, 18, 22, 23, 24, 25, 26, 27, 28, 31, 32, 33, 34, 36]</t>
+          <t>[0, 1, 3, 4, 7, 8, 9, 10, 15, 16, 18, 20, 21, 22, 23, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 41, 42]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0.6339285714285714</t>
+          <t>0.8648351648351649</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.07555888033910928</t>
+          <t>0.07446945936310029</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.07537832042688594</t>
+          <t>0.07216345128545935</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.9158410417742718</t>
+          <t>0.928815181279792</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2.5576493740081787</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.060765743255615</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>[0, 4, 5, 7, 13, 15, 16, 20, 23, 24, 25, 26, 27, 28, 31, 32, 33, 35, 36, 37, 39, 42]</t>
+          <t>[2, 3, 7, 8, 9, 10, 11, 13, 14, 15, 16, 17, 18, 19, 22, 24, 25, 30, 33, 40, 43]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>0.7621031746031746</t>
+          <t>0.679120879120879</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.07961866348797973</t>
+          <t>0.07693449424246573</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.052278387669093394</t>
+          <t>0.12779543289357814</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.9595189463304691</t>
+          <t>0.7767541167124079</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2.4768426418304443</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.167216777801514</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>[0, 3, 6, 7, 15, 16, 17, 19, 23, 25, 30, 31, 32, 33, 36, 37, 38, 43]</t>
+          <t>[1, 2, 5, 9, 10, 12, 15, 18, 19, 20, 23, 24, 26, 31, 33, 35, 36, 37, 38, 40]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>0.6422619047619048</t>
+          <t>0.3835164835164835</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0.07151924417082291</t>
+          <t>0.07099454285947861</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.07749785401057871</t>
+          <t>0.1469931884127146</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.9110416351459691</t>
+          <t>0.7046430377004189</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2.5867741107940674</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>5.236470699310303</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>[2, 9, 11, 13, 15, 16, 18, 19, 22, 23, 24, 25, 27, 28, 30, 31, 32, 33, 34, 35, 37, 41, 44]</t>
+          <t>[1, 2, 4, 7, 8, 9, 10, 11, 12, 14, 16, 17, 18, 19, 20, 21, 24, 25, 26, 28, 30, 33, 34, 36, 37, 39, 40, 43]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0.827579365079365</t>
+          <t>1.0142857142857142</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.0756366388643134</t>
+          <t>0.07387355792011145</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.0624200409834075</t>
+          <t>0.1129675535499811</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.9422894069587265</t>
+          <t>0.8255543117145746</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2.5899147987365723</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.240466117858887</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 8, 13, 15, 16, 18, 21, 25, 26, 28, 29, 30, 31, 34, 35, 36, 41]</t>
+          <t>[1, 3, 4, 5, 8, 9, 11, 12, 16, 17, 19, 21, 24, 26, 29, 30, 31, 32, 33, 35, 36, 39, 41, 42]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>0.473015873015873</t>
+          <t>0.9565934065934066</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.08595191259962637</t>
+          <t>0.07435006564427118</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.09467627711443143</t>
+          <t>0.13460519000800786</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0.8672331099059336</t>
+          <t>0.7523282897587751</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2.51324200630188</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>5.407214164733887</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>[3, 8, 9, 11, 12, 16, 17, 18, 21, 22, 24, 27, 32, 33, 35, 36, 39, 40, 41, 44]</t>
+          <t>[0, 2, 4, 5, 6, 9, 15, 16, 17, 18, 19, 20, 24, 26, 27, 28, 29, 32, 33, 35, 36, 37, 39, 40, 41]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>0.6055555555555556</t>
+          <t>0.8340659340659341</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0.07116249069558439</t>
+          <t>0.07490046309841983</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.05863656604517271</t>
+          <t>0.15091470596775342</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.9490734219217104</t>
+          <t>0.6886736241513794</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2.604325294494629</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>5.092112064361572</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>[6, 9, 13, 15, 20, 25, 26, 31, 32, 33, 35, 36, 43, 44]</t>
+          <t>[1, 2, 3, 7, 8, 9, 10, 11, 13, 14, 15, 17, 18, 19, 20, 23, 24, 28, 30, 32, 33, 35, 37, 43]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0.385515873015873</t>
+          <t>0.8082417582417583</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0.07701586502960428</t>
+          <t>0.0764299270581463</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.055734577407279134</t>
+          <t>0.10498196286803957</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0.9539895094770782</t>
+          <t>0.8493454788386537</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2.4606592655181885</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.095139026641846</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>[0, 1, 5, 6, 9, 10, 11, 14, 15, 16, 17, 21, 27, 29, 31, 33, 34, 35, 36, 37, 41, 43, 44]</t>
+          <t>[2, 4, 5, 6, 9, 16, 17, 18, 19, 21, 22, 25, 26, 27, 28, 35, 37, 39, 40]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0.6857142857142857</t>
+          <t>0.6005494505494505</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0.0801300076819128</t>
+          <t>0.07603205294900613</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0.06656441292018214</t>
+          <t>0.13266143238174335</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0.9343716251115181</t>
+          <t>0.7594296186624296</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2.548666000366211</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.367923259735107</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>[4, 5, 6, 7, 14, 15, 22, 23, 24, 25, 27, 32, 35, 36, 37, 38, 39]</t>
+          <t>[1, 3, 4, 10, 11, 12, 16, 17, 18, 19, 22, 26, 28, 29, 30, 31, 32, 34, 36, 37, 39, 41, 42, 43]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>0.5009920634920635</t>
+          <t>1.1351648351648351</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0.08024051866511236</t>
+          <t>0.07519794368634584</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0.064241821749084</t>
+          <t>0.10063682364477232</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0.9388715851128397</t>
+          <t>0.8615583923154702</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2.513615131378174</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>5.228442668914795</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>[0, 3, 15, 18, 24, 27, 30, 31, 33, 34, 42, 44]</t>
+          <t>[1, 2, 5, 6, 9, 10, 12, 15, 16, 18, 19, 20, 21, 22, 23, 24, 25, 26, 29, 31, 33, 35, 37, 41]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0.05833333333333333</t>
+          <t>0.41923076923076924</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0.07728459233984575</t>
+          <t>0.07596156836082113</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0.10585092528243004</t>
+          <t>0.09864706042870361</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0.8340425490288147</t>
+          <t>0.8669787303192258</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2.502197504043579</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>5.157353401184082</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>[0, 1, 7, 9, 10, 15, 29, 30, 31, 33, 34, 36, 37, 44]</t>
+          <t>[1, 2, 11, 12, 14, 22, 24, 25, 26, 27, 28, 30, 31, 32, 33, 34, 35, 36, 37, 40, 42]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>0.2950396825396825</t>
+          <t>0.7417582417582418</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0.07535178515451205</t>
+          <t>0.07680801540478113</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0.05292249887458012</t>
+          <t>0.12817780529152212</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0.9585152838427947</t>
+          <t>0.7754161851798353</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2.586012363433838</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.488644361495972</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 5, 8, 11, 12, 17, 18, 19, 20, 24, 26, 27, 31, 32, 34, 35, 37, 38, 42, 43]</t>
+          <t>[3, 15, 16, 18, 23, 24, 25, 28, 30, 33, 36, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>0.6839285714285714</t>
+          <t>0.1813186813186813</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.07947210695641008</t>
+          <t>0.07701891425861473</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0.07471319913180575</t>
+          <t>0.0942828112468425</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0.9173196885668127</t>
+          <t>0.8784883720930232</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2.591775417327881</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.344078540802002</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>[2, 5, 8, 9, 11, 12, 13, 14, 16, 17, 18, 19, 21, 23, 25, 27, 28, 32, 33, 35, 37, 38, 39, 40, 42]</t>
+          <t>[0, 2, 3, 6, 8, 9, 11, 12, 13, 15, 16, 17, 18, 20, 21, 25, 26, 29, 31, 32, 33, 35, 36, 37, 41, 42, 43]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1.0682539682539682</t>
+          <t>0.9109890109890111</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0.08566339515960683</t>
+          <t>0.07520124608788441</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0.07143817206088274</t>
+          <t>0.11194096025909098</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0.9244093456042322</t>
+          <t>0.8287104578939766</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2.564091682434082</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.542318105697632</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 7, 8, 10, 12, 15, 16, 17, 18, 19, 20, 22, 27, 28, 32, 34, 35, 36, 37, 38, 39, 44]</t>
+          <t>[0, 1, 3, 5, 6, 8, 9, 12, 14, 16, 17, 18, 21, 23, 26, 28, 30, 31, 33, 35, 36, 37, 40, 41, 43, 44]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1.0555555555555554</t>
+          <t>0.8901098901098901</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.07858900761442053</t>
+          <t>0.06972053824502916</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0.10502378954320012</t>
+          <t>0.13676922088853857</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.8366260506174579</t>
+          <t>0.7443007005633395</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2.553330898284912</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>4.5143561363220215</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>[4, 5, 6, 7, 14, 15, 16, 17, 19, 20, 23, 28, 30, 32, 33, 34, 35, 37, 40]</t>
+          <t>[0, 2, 3, 4, 5, 6, 7, 14, 16, 17, 20, 21, 22, 23, 26, 28, 31, 33, 34, 36, 41]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>0.5327380952380952</t>
+          <t>0.39615384615384613</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0.07907023711040949</t>
+          <t>0.07808175162341809</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0.05967596393022264</t>
+          <t>0.1364063336027205</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0.9472519603700051</t>
+          <t>0.7456557850642784</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2.504486322402954</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.7129552364349365</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>[3, 8, 14, 15, 17, 19, 22, 23, 24, 26, 27, 29, 34, 36, 37, 40, 41, 44]</t>
+          <t>[2, 3, 4, 12, 13, 14, 16, 17, 18, 20, 22, 23, 24, 26, 28, 29, 31, 34, 35, 36, 38, 39, 40, 43]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>0.5551587301587302</t>
+          <t>0.44670329670329667</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.07381850066212031</t>
+          <t>0.07242301931392203</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0.09917355396098738</t>
+          <t>0.13150238017855184</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0.8543202485483089</t>
+          <t>0.7636149429438105</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2.622666835784912</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.668290138244629</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 4, 8, 10, 15, 16, 17, 19, 23, 27, 31, 32, 37, 40, 43]</t>
+          <t>[1, 2, 3, 6, 7, 9, 10, 11, 14, 16, 18, 19, 24, 29, 30, 31, 32, 33, 34, 35, 36, 37, 39, 41, 42]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>0.5093253968253968</t>
+          <t>0.9263736263736264</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.07840231009383308</t>
+          <t>0.07450469786766574</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0.09674125467300114</t>
+          <t>0.13217340002818373</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0.8613784120611667</t>
+          <t>0.7611963744041601</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2.547269105911255</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>4.987611770629883</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>[1, 3, 8, 9, 12, 16, 17, 22, 26, 29, 30, 31, 32, 33, 34, 35, 37, 38, 40, 44]</t>
+          <t>[1, 2, 3, 8, 9, 11, 12, 13, 14, 15, 17, 18, 20, 26, 27, 28, 29, 30, 31, 32, 35, 37, 38, 39, 42, 43]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0.4113095238095238</t>
+          <t>0.9082417582417583</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.06949266774200966</t>
+          <t>0.0776305640433762</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0.09058423180136788</t>
+          <t>0.1313161735742297</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.878461842130434</t>
+          <t>0.7642839087100968</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2.5956008434295654</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>5.232575178146362</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>[10, 12, 13, 16, 19, 20, 25, 26, 31, 34, 35, 36, 37, 38, 40, 44]</t>
+          <t>[1, 3, 5, 7, 12, 15, 16, 17, 18, 19, 22, 24, 25, 29, 31, 33, 35, 37, 39, 43]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0.38650793650793647</t>
+          <t>0.639010989010989</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.07563658252614412</t>
+          <t>0.07249304113930172</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0.08340076595991806</t>
+          <t>0.11027512125954131</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.8969738391253158</t>
+          <t>0.8337705835620396</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2.629020929336548</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>5.260547876358032</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>[2, 3, 9, 16, 18, 19, 22, 23, 24, 28, 29, 35, 36, 37, 39, 41]</t>
+          <t>[0, 1, 3, 5, 6, 9, 11, 13, 14, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 29, 30, 31, 32, 33, 35, 39, 42, 43]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>0.6176587301587302</t>
+          <t>0.9868131868131869</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.07436547365894318</t>
+          <t>0.07362969549337003</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0.07650924197890824</t>
+          <t>0.08821127774326189</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.9132967780195089</t>
+          <t>0.8936344431604796</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2.4832956790924072</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.6822350025177</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>[0, 2, 4, 9, 11, 13, 16, 17, 21, 23, 24, 26, 27, 29, 30, 31, 32, 35, 36, 37, 42, 44]</t>
+          <t>[0, 2, 3, 5, 6, 7, 9, 12, 15, 17, 18, 19, 20, 23, 24, 26, 27, 28, 33, 35, 36, 37, 39, 41, 42]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0.5267857142857143</t>
+          <t>0.8494505494505495</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.07724095455023147</t>
+          <t>0.07490928770271818</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0.054025413853610274</t>
+          <t>0.14698465147926879</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0.9567681676605468</t>
+          <t>0.7046773436371515</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2.594954490661621</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.5776166915893555</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>[3, 8, 9, 10, 11, 14, 16, 19, 22, 25, 28, 29, 31, 32, 35, 37, 43, 44]</t>
+          <t>[0, 1, 2, 3, 4, 7, 8, 9, 10, 12, 13, 14, 16, 17, 22, 25, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 39]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.7942460317460317</t>
+          <t>1.0846153846153845</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.07564201666798584</t>
+          <t>0.0772864643658182</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0.09316149256323827</t>
+          <t>0.11968265231643434</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.8714475630370475</t>
+          <t>0.8041988660985122</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2.5492913722991943</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.733970880508423</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>[2, 4, 7, 9, 10, 13, 16, 17, 18, 19, 22, 29, 31, 33, 34, 37, 42, 43]</t>
+          <t>[0, 1, 7, 8, 9, 10, 14, 15, 16, 18, 20, 21, 24, 27, 29, 31, 32, 35, 37, 40, 41, 43]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0.626984126984127</t>
+          <t>0.3038461538461538</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.07782378599785345</t>
+          <t>0.07672841186976329</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0.0673142469136849</t>
+          <t>0.12173576690152482</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0.9328847177223709</t>
+          <t>0.7974234435938177</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2.5598225593566895</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.6398046016693115</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>[6, 8, 14, 16, 17, 19, 20, 24, 28, 31, 32, 33, 35, 38, 40]</t>
+          <t>[1, 2, 5, 6, 9, 10, 15, 22, 24, 25, 26, 30, 32, 34, 35, 37, 42, 43]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>0.4470238095238095</t>
+          <t>0.4675824175824176</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.0750627751782039</t>
+          <t>0.07190066688750306</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0.08106521412304524</t>
+          <t>0.12919678868440607</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0.9026633250379553</t>
+          <t>0.7718312147912755</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2.63913893699646</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.7922046184539795</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>[2, 3, 7, 8, 10, 16, 19, 21, 25, 27, 28, 31, 34, 35, 36, 38, 41, 44]</t>
+          <t>[2, 3, 6, 11, 15, 16, 19, 22, 25, 26, 28, 30, 31, 34, 35, 37]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.5956349206349206</t>
+          <t>0.35989010989010994</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.07368357560157798</t>
+          <t>0.07609780603053284</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0.11289471147422776</t>
+          <t>0.07053961705077864</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0.8112205857545578</t>
+          <t>0.9319827627714382</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2.612994909286499</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.645263195037842</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 5, 7, 15, 18, 19, 20, 25, 26, 27, 30, 31, 33, 34, 35, 36, 37, 38, 42, 44]</t>
+          <t>[3, 10, 12, 14, 16, 18, 19, 20, 23, 26, 27, 28, 29, 30, 31, 35, 36, 41, 42, 43]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0.6218253968253968</t>
+          <t>0.45219780219780226</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.07331900356777166</t>
+          <t>0.0774959304747663</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0.05969698769833311</t>
+          <t>0.09812413613287291</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0.9472147876852764</t>
+          <t>0.8683852737252636</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2.617692232131958</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.757818222045898</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>[0, 3, 4, 7, 8, 10, 12, 14, 15, 17, 20, 23, 24, 25, 26, 27, 29, 31, 33, 34, 35, 37, 44]</t>
+          <t>[0, 9, 11, 16, 17, 18, 20, 21, 23, 25, 26, 28, 31, 32, 33, 35, 36, 39, 40, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.5111111111111111</t>
+          <t>0.5521978021978022</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.07234211572603966</t>
+          <t>0.07418523896013063</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0.1069848816876048</t>
+          <t>0.10409369338654764</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0.8304677758474068</t>
+          <t>0.8518841181568684</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2.5339322090148926</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>5.026027679443359</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>[1, 3, 8, 11, 14, 15, 16, 17, 18, 20, 24, 26, 27, 28, 29, 31, 33, 35, 40, 41]</t>
+          <t>[1, 2, 5, 7, 9, 13, 15, 19, 21, 22, 23, 25, 31, 32, 36, 41, 43]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.5511904761904762</t>
+          <t>0.31648351648351647</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.07686082747168307</t>
+          <t>0.07599012797208934</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0.07885684945768268</t>
+          <t>0.1381612982844588</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0.907894347838941</t>
+          <t>0.7390690452116135</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2.4604904651641846</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.742700099945068</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 6, 14, 15, 16, 17, 20, 21, 25, 28, 30, 31, 32, 34, 35, 36, 37, 40, 42]</t>
+          <t>[3, 5, 7, 10, 12, 14, 15, 17, 18, 22, 23, 26, 28, 32, 33, 34, 35, 36, 37, 39, 40, 41]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3845,207 +3440,182 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.5559523809523809</t>
+          <t>0.6956043956043956</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0.07899322303141258</t>
+          <t>0.07142322052054846</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0.06252159058044206</t>
+          <t>0.13200240008592143</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0.9421014783859316</t>
+          <t>0.7618138812653474</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2.6114094257354736</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.642048358917236</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>[2, 3, 7, 9, 12, 15, 16, 17, 19, 20, 21, 22, 23, 27, 31, 32, 33, 34, 36, 42, 44]</t>
+          <t>[0, 1, 2, 3, 5, 9, 12, 14, 16, 17, 18, 19, 20, 21, 24, 26, 29, 30, 31, 32, 33, 35, 37, 39, 41, 44]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.5438492063492063</t>
+          <t>0.7060439560439561</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0.07562737200055836</t>
+          <t>0.0747029289125812</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0.06634726724584031</t>
+          <t>0.14898580373430037</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>0.9347991109858979</t>
+          <t>0.6965811425682508</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2.5271377563476562</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.5359649658203125</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>[3, 4, 7, 10, 11, 12, 13, 14, 16, 17, 25, 27, 28, 30, 31, 32, 34, 35, 36]</t>
+          <t>[1, 2, 10, 11, 14, 17, 19, 20, 26, 31, 33, 35, 37, 39, 42, 43]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.5880952380952381</t>
+          <t>0.41923076923076924</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0.0693516944511284</t>
+          <t>0.07170682824961698</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0.09291234863273914</t>
+          <t>0.13831561271584678</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0.8721342251299522</t>
+          <t>0.7384858442871587</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2.544938087463379</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.756549119949341</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>[0, 1, 8, 11, 12, 15, 17, 18, 20, 22, 23, 25, 26, 28, 30, 35, 36, 37, 39, 41, 44]</t>
+          <t>[1, 4, 6, 10, 11, 15, 17, 18, 22, 24, 25, 26, 28, 30, 31, 32, 33, 34, 38, 39]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.9341269841269841</t>
+          <t>0.6032967032967034</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.07215237499422325</t>
+          <t>0.07347736939824252</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0.1094642217886456</t>
+          <t>0.09196513135406928</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0.8225190167629244</t>
+          <t>0.8843889932110357</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2.5307564735412598</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.891864061355591</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>[2, 3, 10, 12, 13, 14, 16, 17, 19, 20, 22, 23, 25, 26, 27, 28, 29, 34, 35, 36, 37, 40, 42, 44]</t>
+          <t>[2, 4, 7, 8, 9, 13, 14, 16, 17, 19, 20, 22, 23, 24, 25, 26, 28, 30, 31, 33, 34, 35, 41]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0.9444444444444444</t>
+          <t>0.4593406593406593</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0.07902773214586253</t>
+          <t>0.07461109339698736</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0.11288977132713106</t>
+          <t>0.09125284972963192</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0.8112371069477704</t>
+          <t>0.8861729019211324</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2.5783605575561523</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>4.539360284805298</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>[1, 2, 4, 5, 6, 14, 16, 17, 19, 21, 22, 24, 25, 26, 27, 29, 30, 32, 33, 34, 35, 36, 37, 39, 42, 44]</t>
+          <t>[0, 1, 3, 4, 5, 8, 9, 13, 15, 17, 18, 20, 22, 23, 26, 27, 30, 32, 33, 34, 35, 36, 37, 39, 42, 43]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4055,620 +3625,545 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0.9541666666666666</t>
+          <t>0.8593406593406593</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.0739424395557062</t>
+          <t>0.07607955946407516</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0.09419700139881483</t>
+          <t>0.11041158634786</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0.8685739079926056</t>
+          <t>0.833358912321248</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2.62141489982605</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.510551452636719</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>[0, 6, 7, 8, 9, 11, 14, 15, 25, 27, 28, 31, 32, 33, 34, 40, 42, 44]</t>
+          <t>[2, 3, 4, 5, 6, 7, 8, 11, 15, 16, 19, 21, 22, 24, 26, 31, 32, 34, 35, 36, 37, 40, 42]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>0.6162698412698413</t>
+          <t>0.8923076923076922</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.0791995390398971</t>
+          <t>0.07612628750330047</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0.11049111314774077</t>
+          <t>0.08209577809371879</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>0.8191734751373433</t>
+          <t>0.9078714069045212</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2.6252834796905518</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>4.773674011230469</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>[0, 6, 9, 13, 15, 16, 24, 25, 26, 29, 30, 31, 32, 33, 34, 36, 37, 40]</t>
+          <t>[0, 4, 5, 8, 10, 12, 14, 15, 16, 18, 21, 23, 25, 26, 27, 30, 31, 33, 34, 35, 37, 39, 43]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>0.4220238095238095</t>
+          <t>0.42912087912087915</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.0675131110084923</t>
+          <t>0.0794401689711138</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0.06128392968929974</t>
+          <t>0.0719457631536257</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0.9443710773035325</t>
+          <t>0.9292440054889499</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2.6200671195983887</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.700540781021118</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 5, 7, 8, 10, 11, 12, 14, 16, 17, 18, 19, 24, 25, 26, 27, 29, 30, 31, 32, 33, 34, 35, 40]</t>
+          <t>[2, 3, 6, 7, 9, 14, 16, 17, 18, 20, 21, 25, 26, 29, 30, 33, 35, 36, 39]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>0.7244047619047619</t>
+          <t>0.260989010989011</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0.08012563147944787</t>
+          <t>0.07143830808464982</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0.09487322477072975</t>
+          <t>0.1360101910484194</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0.8666801662205945</t>
+          <t>0.7471309403437816</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2.617757797241211</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>4.579351902008057</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>[0, 6, 7, 9, 10, 13, 15, 17, 19, 24, 27, 29, 30, 31, 32, 33, 35, 37, 42, 43]</t>
+          <t>[1, 4, 5, 6, 11, 12, 15, 18, 19, 23, 24, 26, 31, 32, 33, 35, 36, 40, 43]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>0.5146825396825396</t>
+          <t>0.41923076923076924</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0.07782828043532355</t>
+          <t>0.06648038790010923</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0.06154953889722606</t>
+          <t>0.08621128403425214</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0.9438878324020598</t>
+          <t>0.8984029683663152</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2.495033025741577</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.668255567550659</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>[1, 5, 6, 9, 15, 17, 18, 19, 21, 24, 27, 28, 33, 35, 36, 37, 41, 43, 44]</t>
+          <t>[2, 5, 7, 11, 14, 16, 18, 23, 24, 26, 30, 32, 33, 34, 35, 36, 37, 40, 42, 43, 44]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>0.6857142857142857</t>
+          <t>0.6901098901098901</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0.07977878793728024</t>
+          <t>0.07502406242435397</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0.07010342433165792</t>
+          <t>0.10628274230046317</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0.9272076227046411</t>
+          <t>0.8455889787664308</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2.621159553527832</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>4.492090940475464</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>[2, 8, 11, 12, 16, 23, 25, 26, 27, 30, 32, 36, 37, 38, 43]</t>
+          <t>[1, 2, 3, 4, 5, 17, 18, 22, 23, 26, 28, 29, 31, 33, 34, 35, 36, 37, 40, 41, 43]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>0.4299603174603175</t>
+          <t>0.5318681318681319</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>0.0700529454103201</t>
+          <t>0.07074767270778123</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0.07690276715662188</t>
+          <t>0.13194535085754808</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>0.9124025684368691</t>
+          <t>0.7620197168857432</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2.623934030532837</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.778129577636719</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>[4, 5, 8, 9, 11, 12, 13, 14, 15, 16, 17, 19, 23, 27, 28, 31, 34, 35, 36, 37, 38, 40, 41, 44]</t>
+          <t>[1, 3, 4, 11, 13, 15, 16, 18, 25, 26, 33, 34, 36, 40, 42, 43]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>0.9305555555555556</t>
+          <t>0.4675824175824176</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.08220318420279958</t>
+          <t>0.06990990847017867</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0.1166831423185289</t>
+          <t>0.0888844126416419</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>0.798338185346919</t>
+          <t>0.8920049111656796</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2.49723744392395</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>4.493035078048706</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>[0, 1, 2, 3, 5, 6, 8, 12, 15, 22, 23, 28, 30, 32, 33, 34, 35, 36, 39, 40, 41, 43, 44]</t>
+          <t>[0, 1, 3, 6, 10, 11, 14, 15, 16, 17, 20, 22, 23, 24, 26, 29, 31, 32, 33, 34, 35, 39, 40, 42, 43]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>0.8823412698412698</t>
+          <t>0.6087912087912088</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0.08261762145829969</t>
+          <t>0.07304427630623893</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0.10985899799764452</t>
+          <t>0.10598124713805407</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>0.821236559139785</t>
+          <t>0.8464637801531127</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2.63204288482666</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>4.740255117416382</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 5, 7, 8, 11, 12, 14, 17, 19, 21, 22, 23, 24, 25, 27, 28, 29, 30, 33, 36, 37, 38, 41, 42]</t>
+          <t>[0, 1, 3, 9, 15, 16, 17, 18, 20, 21, 25, 26, 27, 30, 32, 35, 36, 37, 40]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1.2646825396825396</t>
+          <t>0.41208791208791207</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0.07968393033878032</t>
+          <t>0.07306904358349284</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0.10432699480308556</t>
+          <t>0.08027188679031058</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>0.8387867129173123</t>
+          <t>0.9119195074389715</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2.505082607269287</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>4.7252771854400635</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>[1, 7, 15, 17, 19, 23, 25, 27, 29, 30, 32, 34, 35, 36, 38, 41, 42]</t>
+          <t>[2, 7, 8, 9, 14, 16, 19, 21, 22, 23, 24, 27, 29, 31, 32, 33, 35, 40, 43]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>0.5013888888888889</t>
+          <t>0.35714285714285715</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0.07271151731249599</t>
+          <t>0.07654834671268206</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0.07784542453938414</t>
+          <t>0.09331962446528214</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0.9102419061370146</t>
+          <t>0.8809583995377727</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2.613762617111206</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.8340113162994385</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>[3, 8, 11, 18, 20, 24, 26, 27, 33, 34, 35, 36, 37, 39, 40, 41, 44]</t>
+          <t>[1, 4, 8, 9, 11, 12, 13, 15, 17, 20, 21, 23, 24, 25, 26, 27, 30, 31, 34, 35, 36, 38, 39, 43]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>0.47757936507936505</t>
+          <t>0.6005494505494505</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.0658682497707011</t>
+          <t>0.07494164326309574</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0.05645600014347311</t>
+          <t>0.08513474499102879</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>0.9527906903945783</t>
+          <t>0.9009244547161636</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2.5798823833465576</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.623355150222778</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 8, 10, 15, 21, 22, 23, 24, 25, 26, 27, 28, 29, 31, 34, 35, 37, 39, 40, 41, 44]</t>
+          <t>[5, 9, 11, 12, 14, 15, 18, 19, 20, 23, 24, 25, 28, 31, 33, 34, 35, 37, 39, 43, 44]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>0.8378968253968254</t>
+          <t>0.4697802197802198</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>0.0758530963199621</t>
+          <t>0.07373096421195771</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0.1003308695098041</t>
+          <t>0.08054498755860727</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>0.8509003615532704</t>
+          <t>0.9113191535461505</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2.5776689052581787</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>4.739855051040649</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>[3, 7, 9, 11, 14, 15, 19, 23, 27, 28, 29, 30, 31, 33, 35, 36, 37, 44]</t>
+          <t>[2, 5, 8, 9, 11, 15, 16, 17, 18, 19, 20, 21, 22, 24, 25, 26, 27, 32, 33, 34, 35, 37, 38, 39, 42, 43]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>0.6371031746031746</t>
+          <t>0.7818681318681319</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.0687046646029894</t>
+          <t>0.07649972917242326</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0.05788542271027388</t>
+          <t>0.09695989389620156</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>0.9503698193016231</t>
+          <t>0.8714899609995667</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2.6298046112060547</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>4.671451807022095</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 8, 9, 10, 11, 13, 14, 15, 16, 17, 18, 19, 22, 26, 27, 31, 32, 33, 34, 35, 37, 39, 41, 43, 44]</t>
+          <t>[1, 2, 3, 6, 9, 10, 11, 13, 16, 17, 18, 20, 22, 24, 30, 32, 34, 36, 37, 38, 39, 40, 42]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1.2251984126984126</t>
+          <t>0.7725274725274726</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.07952800710438912</t>
+          <t>0.08014842499433093</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0.0913473401906042</t>
+          <t>0.1347635765123678</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>0.876405469862735</t>
+          <t>0.7517450888343203</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2.5875511169433594</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>4.640889883041382</t>
         </is>
       </c>
     </row>
